--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122582226</v>
+        <v>122582224</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462329</v>
+        <v>462388</v>
       </c>
       <c r="R4" t="n">
-        <v>7101753</v>
+        <v>7101758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122582215</v>
+        <v>122582220</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462274</v>
+        <v>462633</v>
       </c>
       <c r="R5" t="n">
-        <v>7101504</v>
+        <v>7101730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122582220</v>
+        <v>122582217</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462633</v>
+        <v>462228</v>
       </c>
       <c r="R6" t="n">
-        <v>7101730</v>
+        <v>7101556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122582229</v>
+        <v>122582227</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462029</v>
+        <v>462139</v>
       </c>
       <c r="R7" t="n">
-        <v>7101397</v>
+        <v>7101622</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122582221</v>
+        <v>122582225</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462498</v>
+        <v>462387</v>
       </c>
       <c r="R8" t="n">
-        <v>7101810</v>
+        <v>7101761</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122582225</v>
+        <v>122582219</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462387</v>
+        <v>462241</v>
       </c>
       <c r="R9" t="n">
-        <v>7101761</v>
+        <v>7101586</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122582223</v>
+        <v>122582228</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462387</v>
+        <v>462116</v>
       </c>
       <c r="R10" t="n">
-        <v>7101748</v>
+        <v>7101595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122582219</v>
+        <v>122582229</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462241</v>
+        <v>462029</v>
       </c>
       <c r="R11" t="n">
-        <v>7101586</v>
+        <v>7101397</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122582234</v>
+        <v>122582226</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461995</v>
+        <v>462329</v>
       </c>
       <c r="R12" t="n">
-        <v>7101417</v>
+        <v>7101753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122582233</v>
+        <v>122582221</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462707</v>
+        <v>462498</v>
       </c>
       <c r="R13" t="n">
-        <v>7101870</v>
+        <v>7101810</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122582228</v>
+        <v>122582234</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462116</v>
+        <v>461995</v>
       </c>
       <c r="R14" t="n">
-        <v>7101595</v>
+        <v>7101417</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122582227</v>
+        <v>122582214</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462139</v>
+        <v>462302</v>
       </c>
       <c r="R15" t="n">
-        <v>7101622</v>
+        <v>7101479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122582214</v>
+        <v>122582223</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462302</v>
+        <v>462387</v>
       </c>
       <c r="R16" t="n">
-        <v>7101479</v>
+        <v>7101748</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122582224</v>
+        <v>122582215</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462388</v>
+        <v>462274</v>
       </c>
       <c r="R17" t="n">
-        <v>7101758</v>
+        <v>7101504</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122582217</v>
+        <v>122582233</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462228</v>
+        <v>462707</v>
       </c>
       <c r="R18" t="n">
-        <v>7101556</v>
+        <v>7101870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122582224</v>
+        <v>122582229</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462388</v>
+        <v>462029</v>
       </c>
       <c r="R4" t="n">
-        <v>7101758</v>
+        <v>7101397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122582217</v>
+        <v>122582227</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462228</v>
+        <v>462139</v>
       </c>
       <c r="R6" t="n">
-        <v>7101556</v>
+        <v>7101622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122582227</v>
+        <v>122582221</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462139</v>
+        <v>462498</v>
       </c>
       <c r="R7" t="n">
-        <v>7101622</v>
+        <v>7101810</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122582225</v>
+        <v>122582217</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462387</v>
+        <v>462228</v>
       </c>
       <c r="R8" t="n">
-        <v>7101761</v>
+        <v>7101556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122582219</v>
+        <v>122582222</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462241</v>
+        <v>462382</v>
       </c>
       <c r="R9" t="n">
-        <v>7101586</v>
+        <v>7101750</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122582228</v>
+        <v>122582214</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462116</v>
+        <v>462302</v>
       </c>
       <c r="R10" t="n">
-        <v>7101595</v>
+        <v>7101479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122582229</v>
+        <v>122582224</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462029</v>
+        <v>462388</v>
       </c>
       <c r="R11" t="n">
-        <v>7101397</v>
+        <v>7101758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122582226</v>
+        <v>122582233</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462329</v>
+        <v>462707</v>
       </c>
       <c r="R12" t="n">
-        <v>7101753</v>
+        <v>7101870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122582221</v>
+        <v>122582215</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462498</v>
+        <v>462274</v>
       </c>
       <c r="R13" t="n">
-        <v>7101810</v>
+        <v>7101504</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122582214</v>
+        <v>122582226</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462302</v>
+        <v>462329</v>
       </c>
       <c r="R15" t="n">
-        <v>7101479</v>
+        <v>7101753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122582223</v>
+        <v>122582219</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462387</v>
+        <v>462241</v>
       </c>
       <c r="R16" t="n">
-        <v>7101748</v>
+        <v>7101586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122582215</v>
+        <v>122582225</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462274</v>
+        <v>462387</v>
       </c>
       <c r="R17" t="n">
-        <v>7101504</v>
+        <v>7101761</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122582233</v>
+        <v>122582228</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462707</v>
+        <v>462116</v>
       </c>
       <c r="R18" t="n">
-        <v>7101870</v>
+        <v>7101595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,7 +2512,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122582222</v>
+        <v>122582223</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462382</v>
+        <v>462387</v>
       </c>
       <c r="R19" t="n">
-        <v>7101750</v>
+        <v>7101748</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122582229</v>
+        <v>122582217</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462029</v>
+        <v>462228</v>
       </c>
       <c r="R4" t="n">
-        <v>7101397</v>
+        <v>7101556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122582220</v>
+        <v>122582215</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462633</v>
+        <v>462274</v>
       </c>
       <c r="R5" t="n">
-        <v>7101730</v>
+        <v>7101504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122582227</v>
+        <v>122582228</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462139</v>
+        <v>462116</v>
       </c>
       <c r="R6" t="n">
-        <v>7101622</v>
+        <v>7101595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122582217</v>
+        <v>122582224</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462228</v>
+        <v>462388</v>
       </c>
       <c r="R8" t="n">
-        <v>7101556</v>
+        <v>7101758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122582222</v>
+        <v>122582234</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462382</v>
+        <v>461995</v>
       </c>
       <c r="R9" t="n">
-        <v>7101750</v>
+        <v>7101417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122582214</v>
+        <v>122582226</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462302</v>
+        <v>462329</v>
       </c>
       <c r="R10" t="n">
-        <v>7101479</v>
+        <v>7101753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122582224</v>
+        <v>122582233</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462388</v>
+        <v>462707</v>
       </c>
       <c r="R11" t="n">
-        <v>7101758</v>
+        <v>7101870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122582233</v>
+        <v>122582214</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462707</v>
+        <v>462302</v>
       </c>
       <c r="R12" t="n">
-        <v>7101870</v>
+        <v>7101479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122582215</v>
+        <v>122582227</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462274</v>
+        <v>462139</v>
       </c>
       <c r="R13" t="n">
-        <v>7101504</v>
+        <v>7101622</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122582234</v>
+        <v>122582223</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461995</v>
+        <v>462387</v>
       </c>
       <c r="R14" t="n">
-        <v>7101417</v>
+        <v>7101748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122582226</v>
+        <v>122582229</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462329</v>
+        <v>462029</v>
       </c>
       <c r="R15" t="n">
-        <v>7101753</v>
+        <v>7101397</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122582228</v>
+        <v>122582220</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462116</v>
+        <v>462633</v>
       </c>
       <c r="R18" t="n">
-        <v>7101595</v>
+        <v>7101730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,7 +2512,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122582223</v>
+        <v>122582222</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462387</v>
+        <v>462382</v>
       </c>
       <c r="R19" t="n">
-        <v>7101748</v>
+        <v>7101750</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122582217</v>
+        <v>122582229</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462228</v>
+        <v>462029</v>
       </c>
       <c r="R4" t="n">
-        <v>7101556</v>
+        <v>7101397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122582215</v>
+        <v>122582217</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462274</v>
+        <v>462228</v>
       </c>
       <c r="R5" t="n">
-        <v>7101504</v>
+        <v>7101556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122582228</v>
+        <v>122582233</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462116</v>
+        <v>462707</v>
       </c>
       <c r="R6" t="n">
-        <v>7101595</v>
+        <v>7101870</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122582221</v>
+        <v>122582226</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462498</v>
+        <v>462329</v>
       </c>
       <c r="R7" t="n">
-        <v>7101810</v>
+        <v>7101753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122582224</v>
+        <v>122582214</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462388</v>
+        <v>462302</v>
       </c>
       <c r="R8" t="n">
-        <v>7101758</v>
+        <v>7101479</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122582234</v>
+        <v>122582227</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461995</v>
+        <v>462139</v>
       </c>
       <c r="R9" t="n">
-        <v>7101417</v>
+        <v>7101622</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122582226</v>
+        <v>122582223</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462329</v>
+        <v>462387</v>
       </c>
       <c r="R10" t="n">
-        <v>7101753</v>
+        <v>7101748</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122582233</v>
+        <v>122582222</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462707</v>
+        <v>462382</v>
       </c>
       <c r="R11" t="n">
-        <v>7101870</v>
+        <v>7101750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122582214</v>
+        <v>122582215</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462302</v>
+        <v>462274</v>
       </c>
       <c r="R12" t="n">
-        <v>7101479</v>
+        <v>7101504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122582227</v>
+        <v>122582228</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462139</v>
+        <v>462116</v>
       </c>
       <c r="R13" t="n">
-        <v>7101622</v>
+        <v>7101595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122582223</v>
+        <v>122582219</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462387</v>
+        <v>462241</v>
       </c>
       <c r="R14" t="n">
-        <v>7101748</v>
+        <v>7101586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122582229</v>
+        <v>122582224</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462029</v>
+        <v>462388</v>
       </c>
       <c r="R15" t="n">
-        <v>7101397</v>
+        <v>7101758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122582219</v>
+        <v>122582225</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462241</v>
+        <v>462387</v>
       </c>
       <c r="R16" t="n">
-        <v>7101586</v>
+        <v>7101761</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122582225</v>
+        <v>122582221</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462387</v>
+        <v>462498</v>
       </c>
       <c r="R17" t="n">
-        <v>7101761</v>
+        <v>7101810</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122582222</v>
+        <v>122582234</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462382</v>
+        <v>461995</v>
       </c>
       <c r="R19" t="n">
-        <v>7101750</v>
+        <v>7101417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122582221</v>
+        <v>122582234</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,21 +2314,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462498</v>
+        <v>461995</v>
       </c>
       <c r="R17" t="n">
-        <v>7101810</v>
+        <v>7101417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122582220</v>
+        <v>122582221</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462633</v>
+        <v>462498</v>
       </c>
       <c r="R18" t="n">
-        <v>7101730</v>
+        <v>7101810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122582234</v>
+        <v>122582220</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461995</v>
+        <v>462633</v>
       </c>
       <c r="R19" t="n">
-        <v>7101417</v>
+        <v>7101730</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122582234</v>
+        <v>122582221</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,21 +2314,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461995</v>
+        <v>462498</v>
       </c>
       <c r="R17" t="n">
-        <v>7101417</v>
+        <v>7101810</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122582221</v>
+        <v>122582220</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462498</v>
+        <v>462633</v>
       </c>
       <c r="R18" t="n">
-        <v>7101810</v>
+        <v>7101730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122582220</v>
+        <v>122582234</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462633</v>
+        <v>461995</v>
       </c>
       <c r="R19" t="n">
-        <v>7101730</v>
+        <v>7101417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 62136-2024 artfynd.xlsx
+++ b/artfynd/A 62136-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122582229</v>
+        <v>122582226</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462029</v>
+        <v>462329</v>
       </c>
       <c r="R4" t="n">
-        <v>7101397</v>
+        <v>7101753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122582217</v>
+        <v>122582233</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462228</v>
+        <v>462707</v>
       </c>
       <c r="R5" t="n">
-        <v>7101556</v>
+        <v>7101870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122582233</v>
+        <v>122582214</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462707</v>
+        <v>462302</v>
       </c>
       <c r="R6" t="n">
-        <v>7101870</v>
+        <v>7101479</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122582226</v>
+        <v>122582228</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462329</v>
+        <v>462116</v>
       </c>
       <c r="R7" t="n">
-        <v>7101753</v>
+        <v>7101595</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122582214</v>
+        <v>122582221</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462302</v>
+        <v>462498</v>
       </c>
       <c r="R8" t="n">
-        <v>7101479</v>
+        <v>7101810</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122582227</v>
+        <v>122582220</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462139</v>
+        <v>462633</v>
       </c>
       <c r="R9" t="n">
-        <v>7101622</v>
+        <v>7101730</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122582223</v>
+        <v>122582229</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462387</v>
+        <v>462029</v>
       </c>
       <c r="R10" t="n">
-        <v>7101748</v>
+        <v>7101397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122582222</v>
+        <v>122582225</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462382</v>
+        <v>462387</v>
       </c>
       <c r="R11" t="n">
-        <v>7101750</v>
+        <v>7101761</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122582215</v>
+        <v>122582219</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462274</v>
+        <v>462241</v>
       </c>
       <c r="R12" t="n">
-        <v>7101504</v>
+        <v>7101586</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122582228</v>
+        <v>122582227</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462116</v>
+        <v>462139</v>
       </c>
       <c r="R13" t="n">
-        <v>7101595</v>
+        <v>7101622</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122582219</v>
+        <v>122582222</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462241</v>
+        <v>462382</v>
       </c>
       <c r="R14" t="n">
-        <v>7101586</v>
+        <v>7101750</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122582224</v>
+        <v>122582217</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462388</v>
+        <v>462228</v>
       </c>
       <c r="R15" t="n">
-        <v>7101758</v>
+        <v>7101556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122582225</v>
+        <v>122582223</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2234,7 +2234,7 @@
         <v>462387</v>
       </c>
       <c r="R16" t="n">
-        <v>7101761</v>
+        <v>7101748</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122582221</v>
+        <v>122582215</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462498</v>
+        <v>462274</v>
       </c>
       <c r="R17" t="n">
-        <v>7101810</v>
+        <v>7101504</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122582220</v>
+        <v>122582234</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462633</v>
+        <v>461995</v>
       </c>
       <c r="R18" t="n">
-        <v>7101730</v>
+        <v>7101417</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122582234</v>
+        <v>122582224</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461995</v>
+        <v>462388</v>
       </c>
       <c r="R19" t="n">
-        <v>7101417</v>
+        <v>7101758</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
